--- a/data/raw/Monitoreo/Monitoreo_Informacion_Procesos 2025.xlsx
+++ b/data/raw/Monitoreo/Monitoreo_Informacion_Procesos 2025.xlsx
@@ -2559,18 +2559,18 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2887,6 +2887,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3186,21 +3190,21 @@
   <sheetData>
     <row r="1" spans="2:4" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="61" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
     </row>
     <row r="3" spans="2:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="64" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="62"/>
       <c r="D3" s="62"/>
     </row>
     <row r="5" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="65" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="62"/>
@@ -3210,7 +3214,7 @@
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="63" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="62"/>
@@ -3219,7 +3223,7 @@
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="63" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="62"/>
@@ -3228,7 +3232,7 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="63" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="62"/>
@@ -3237,7 +3241,7 @@
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="63" t="s">
         <v>10</v>
       </c>
       <c r="D9" s="62"/>
@@ -3246,7 +3250,7 @@
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="63" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="62"/>
@@ -3255,7 +3259,7 @@
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="63" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="62"/>
@@ -3264,7 +3268,7 @@
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="63" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="62"/>
@@ -3273,13 +3277,13 @@
       <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="61" t="s">
+      <c r="C13" s="63" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="62"/>
     </row>
     <row r="15" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="66" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="62"/>
@@ -3289,7 +3293,7 @@
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="61" t="s">
+      <c r="C16" s="63" t="s">
         <v>21</v>
       </c>
       <c r="D16" s="62"/>
@@ -3298,7 +3302,7 @@
       <c r="B17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="C17" s="63" t="s">
         <v>23</v>
       </c>
       <c r="D17" s="62"/>
@@ -3307,7 +3311,7 @@
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="63" t="s">
         <v>25</v>
       </c>
       <c r="D18" s="62"/>
@@ -3316,7 +3320,7 @@
       <c r="B19" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="63" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="62"/>
@@ -3325,13 +3329,14 @@
       <c r="B20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="61" t="s">
+      <c r="C20" s="63" t="s">
         <v>29</v>
       </c>
       <c r="D20" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C12:D12"/>
@@ -3348,7 +3353,6 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16195,6 +16199,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101004B3553A73F55864994CAF6806DB2233B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="484b429f64a896cf9121b5ac5a445701">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="787dcc16-ad9c-4aed-8595-d8b714944830" xmlns:ns3="eb4e1f33-0654-4877-a695-74ac1243131b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd883e4f23756e7d91dbb93f630d1c1d" ns2:_="" ns3:_="">
     <xsd:import namespace="787dcc16-ad9c-4aed-8595-d8b714944830"/>
@@ -16429,15 +16442,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE9DE103-2370-4EAB-B038-A3D7F13C5755}">
   <ds:schemaRefs>
@@ -16450,6 +16454,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7E9B958-9418-4A98-8F85-D5A77DEB1930}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54CB6253-086C-4DD9-9A75-7616EB60A558}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16466,12 +16478,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7E9B958-9418-4A98-8F85-D5A77DEB1930}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>